--- a/Res_ConvLSTM/DroughtDataset_model_testing_1753960290_h_11.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1753960290_h_11.xlsx
@@ -652,13 +652,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.03251349487226771</v>
+        <v>0.02822642604242095</v>
       </c>
       <c r="B2" t="n">
-        <v>0.008471071234002286</v>
+        <v>0.008464239976449508</v>
       </c>
       <c r="C2" t="n">
-        <v>69259047</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>69259047</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>46110244</v>
+        <v>3685087</v>
       </c>
       <c r="L2" t="n">
-        <v>23694058</v>
+        <v>1761827</v>
       </c>
       <c r="M2" t="n">
-        <v>5381209</v>
+        <v>363187</v>
       </c>
       <c r="N2" t="n">
-        <v>209110</v>
+        <v>8170</v>
       </c>
       <c r="O2" t="n">
-        <v>3213376</v>
+        <v>193133</v>
       </c>
       <c r="P2" t="n">
-        <v>1168192</v>
+        <v>685</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999751448631287</v>
+        <v>0.9999673962593079</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8125253319740295</v>
+        <v>0.7340233325958252</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6593999862670898</v>
+        <v>0.5180396437644958</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5701825022697449</v>
+        <v>0.3859556913375854</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1891482472419739</v>
+        <v>0.04821652173995972</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6248908042907715</v>
+        <v>0.3997487127780914</v>
       </c>
       <c r="W2" t="n">
-        <v>0.7675162553787231</v>
+        <v>0.4615902900695801</v>
       </c>
       <c r="X2" t="n">
-        <v>69259047</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,469 +742,469 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>69259047</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>52478774</v>
+        <v>4734132</v>
       </c>
       <c r="AG2" t="n">
-        <v>32815898</v>
+        <v>3030830</v>
       </c>
       <c r="AH2" t="n">
-        <v>8820770</v>
+        <v>808192</v>
       </c>
       <c r="AI2" t="n">
-        <v>649524</v>
+        <v>59360</v>
       </c>
       <c r="AJ2" t="n">
-        <v>5058909</v>
+        <v>461747</v>
       </c>
       <c r="AK2" t="n">
-        <v>1982020</v>
+        <v>180527</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9557238221168518</v>
+        <v>0.9544405341148376</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9118883609771729</v>
+        <v>0.9131393432617188</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8583142161369324</v>
+        <v>0.8580844402313232</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6617491245269775</v>
+        <v>0.660965621471405</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020285606384277</v>
+        <v>0.902009904384613</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314546585083008</v>
+        <v>0.9314878582954407</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.008611155530519134</v>
+        <v>0.007324892457588218</v>
       </c>
       <c r="B3" t="n">
-        <v>0.002031164118261611</v>
+        <v>0.002029011818888065</v>
       </c>
       <c r="C3" t="n">
-        <v>1105</v>
+        <v>21</v>
       </c>
       <c r="D3" t="n">
-        <v>46110244</v>
+        <v>3685087</v>
       </c>
       <c r="E3" t="n">
-        <v>8327279</v>
+        <v>1180732</v>
       </c>
       <c r="F3" t="n">
-        <v>314910</v>
+        <v>67647</v>
       </c>
       <c r="G3" t="n">
-        <v>27514</v>
+        <v>5420</v>
       </c>
       <c r="H3" t="n">
-        <v>23291</v>
+        <v>4975</v>
       </c>
       <c r="I3" t="n">
-        <v>1230</v>
+        <v>74</v>
       </c>
       <c r="J3" t="n">
-        <v>109889630</v>
+        <v>10016416</v>
       </c>
       <c r="K3" t="n">
-        <v>113705769</v>
+        <v>10050336</v>
       </c>
       <c r="L3" t="n">
-        <v>130839857</v>
+        <v>11357962</v>
       </c>
       <c r="M3" t="n">
-        <v>164803454</v>
+        <v>14808024</v>
       </c>
       <c r="N3" t="n">
-        <v>177271406</v>
+        <v>16078366</v>
       </c>
       <c r="O3" t="n">
-        <v>171609115</v>
+        <v>15527094</v>
       </c>
       <c r="P3" t="n">
-        <v>176668005</v>
+        <v>16134869</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8413422703742981</v>
+        <v>0.7453721165657043</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6568573713302612</v>
+        <v>0.5286778807640076</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5229318737983704</v>
+        <v>0.3848314583301544</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2128196656703949</v>
+        <v>0.0908181443810463</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5725533366203308</v>
+        <v>0.3768426775932312</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5488218665122986</v>
+        <v>0.003532165894284844</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>52478774</v>
+        <v>4734132</v>
       </c>
       <c r="Z3" t="n">
-        <v>2158656</v>
+        <v>194580</v>
       </c>
       <c r="AA3" t="n">
-        <v>92853</v>
+        <v>8401</v>
       </c>
       <c r="AB3" t="n">
-        <v>74703</v>
+        <v>6802</v>
       </c>
       <c r="AC3" t="n">
-        <v>257</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>330</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>109891353</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>121913622</v>
+        <v>11159664</v>
       </c>
       <c r="AG3" t="n">
-        <v>139907703</v>
+        <v>12708783</v>
       </c>
       <c r="AH3" t="n">
-        <v>167403857</v>
+        <v>15252180</v>
       </c>
       <c r="AI3" t="n">
-        <v>177835829</v>
+        <v>16209192</v>
       </c>
       <c r="AJ3" t="n">
-        <v>172988579</v>
+        <v>15766935</v>
       </c>
       <c r="AK3" t="n">
-        <v>176875999</v>
+        <v>16122390</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575445055961609</v>
+        <v>0.9575594663619995</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9097371101379395</v>
+        <v>0.9094722867012024</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8571794629096985</v>
+        <v>0.8563569188117981</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6610466837882996</v>
+        <v>0.6598488092422485</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9013869762420654</v>
+        <v>0.9009644985198975</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9311618804931641</v>
+        <v>0.9308778047561646</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.07171313794487856</v>
+        <v>0.0638485780210369</v>
       </c>
       <c r="B4" t="n">
-        <v>0.03202834854031932</v>
+        <v>0.03200610849614379</v>
       </c>
       <c r="C4" t="n">
-        <v>135</v>
+        <v>25</v>
       </c>
       <c r="D4" t="n">
-        <v>9765857</v>
+        <v>1194659</v>
       </c>
       <c r="E4" t="n">
-        <v>23694058</v>
+        <v>1761827</v>
       </c>
       <c r="F4" t="n">
-        <v>2183087</v>
+        <v>306536</v>
       </c>
       <c r="G4" t="n">
-        <v>141651</v>
+        <v>28476</v>
       </c>
       <c r="H4" t="n">
-        <v>264782</v>
+        <v>40881</v>
       </c>
       <c r="I4" t="n">
-        <v>22276</v>
+        <v>111</v>
       </c>
       <c r="J4" t="n">
-        <v>1723</v>
+        <v>206</v>
       </c>
       <c r="K4" t="n">
-        <v>10639058</v>
+        <v>1335308</v>
       </c>
       <c r="L4" t="n">
-        <v>12238697</v>
+        <v>1639123</v>
       </c>
       <c r="M4" t="n">
-        <v>4056487</v>
+        <v>577820</v>
       </c>
       <c r="N4" t="n">
-        <v>896425</v>
+        <v>161274</v>
       </c>
       <c r="O4" t="n">
-        <v>1928924</v>
+        <v>290003</v>
       </c>
       <c r="P4" t="n">
-        <v>353850</v>
+        <v>799</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999875426292419</v>
+        <v>0.9999837279319763</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8266827464103699</v>
+        <v>0.7396541833877563</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6581262350082397</v>
+        <v>0.5233047008514404</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5455359816551208</v>
+        <v>0.3853927552700043</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2002869695425034</v>
+        <v>0.06299055367708206</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5975782871246338</v>
+        <v>0.3879578709602356</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6400023102760315</v>
+        <v>0.007010684814304113</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2270831</v>
+        <v>211204</v>
       </c>
       <c r="Z4" t="n">
-        <v>32815898</v>
+        <v>3030830</v>
       </c>
       <c r="AA4" t="n">
-        <v>911085</v>
+        <v>83661</v>
       </c>
       <c r="AB4" t="n">
-        <v>60790</v>
+        <v>5621</v>
       </c>
       <c r="AC4" t="n">
-        <v>12494</v>
+        <v>1131</v>
       </c>
       <c r="AD4" t="n">
-        <v>748</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2431205</v>
+        <v>225980</v>
       </c>
       <c r="AG4" t="n">
-        <v>3170851</v>
+        <v>288302</v>
       </c>
       <c r="AH4" t="n">
-        <v>1456084</v>
+        <v>133664</v>
       </c>
       <c r="AI4" t="n">
-        <v>332002</v>
+        <v>30448</v>
       </c>
       <c r="AJ4" t="n">
-        <v>549460</v>
+        <v>50162</v>
       </c>
       <c r="AK4" t="n">
-        <v>145856</v>
+        <v>13278</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9566332697868347</v>
+        <v>0.9559974670410156</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9108114838600159</v>
+        <v>0.9113021492958069</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8577464818954468</v>
+        <v>0.8572198748588562</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6613976955413818</v>
+        <v>0.660406768321991</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.901707649230957</v>
+        <v>0.9014868140220642</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313082695007324</v>
+        <v>0.9311826825141907</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>109</v>
+        <v>28</v>
       </c>
       <c r="D5" t="n">
-        <v>627802</v>
+        <v>104082</v>
       </c>
       <c r="E5" t="n">
-        <v>3112133</v>
+        <v>340897</v>
       </c>
       <c r="F5" t="n">
-        <v>5381209</v>
+        <v>363187</v>
       </c>
       <c r="G5" t="n">
-        <v>284688</v>
+        <v>45749</v>
       </c>
       <c r="H5" t="n">
-        <v>807077</v>
+        <v>89688</v>
       </c>
       <c r="I5" t="n">
-        <v>77441</v>
+        <v>125</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>8695329</v>
+        <v>1258869</v>
       </c>
       <c r="L5" t="n">
-        <v>12377788</v>
+        <v>1570688</v>
       </c>
       <c r="M5" t="n">
-        <v>4909250</v>
+        <v>580569</v>
       </c>
       <c r="N5" t="n">
-        <v>773459</v>
+        <v>81790</v>
       </c>
       <c r="O5" t="n">
-        <v>2398985</v>
+        <v>319370</v>
       </c>
       <c r="P5" t="n">
-        <v>960353</v>
+        <v>193247</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999904036521912</v>
+        <v>0.9999873638153076</v>
       </c>
       <c r="R5" t="n">
-        <v>0.8920773267745972</v>
+        <v>0.8411365151405334</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8625931739807129</v>
+        <v>0.8034360408782959</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9499541521072388</v>
+        <v>0.9290620088577271</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9906788468360901</v>
+        <v>0.985115110874176</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9758420586585999</v>
+        <v>0.9626829028129578</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9926642179489136</v>
+        <v>0.9881169199943542</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>88331</v>
+        <v>8137</v>
       </c>
       <c r="Z5" t="n">
-        <v>943632</v>
+        <v>87456</v>
       </c>
       <c r="AA5" t="n">
-        <v>8820770</v>
+        <v>808192</v>
       </c>
       <c r="AB5" t="n">
-        <v>109731</v>
+        <v>10038</v>
       </c>
       <c r="AC5" t="n">
-        <v>321032</v>
+        <v>29300</v>
       </c>
       <c r="AD5" t="n">
-        <v>6963</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2326799</v>
+        <v>209824</v>
       </c>
       <c r="AG5" t="n">
-        <v>3255948</v>
+        <v>301685</v>
       </c>
       <c r="AH5" t="n">
-        <v>1469689</v>
+        <v>135564</v>
       </c>
       <c r="AI5" t="n">
-        <v>333045</v>
+        <v>30600</v>
       </c>
       <c r="AJ5" t="n">
-        <v>553452</v>
+        <v>50756</v>
       </c>
       <c r="AK5" t="n">
-        <v>146525</v>
+        <v>13405</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9734413027763367</v>
+        <v>0.9733120203018188</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9641262292861938</v>
+        <v>0.963870108127594</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9836686253547668</v>
+        <v>0.9835128784179688</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9962877631187439</v>
+        <v>0.9962615370750427</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.993843674659729</v>
+        <v>0.9938199520111084</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.998367965221405</v>
+        <v>0.9983659982681274</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>108</v>
+        <v>19</v>
       </c>
       <c r="D6" t="n">
-        <v>172412</v>
+        <v>20615</v>
       </c>
       <c r="E6" t="n">
-        <v>230456</v>
+        <v>25779</v>
       </c>
       <c r="F6" t="n">
-        <v>249551</v>
+        <v>25796</v>
       </c>
       <c r="G6" t="n">
-        <v>209110</v>
+        <v>8170</v>
       </c>
       <c r="H6" t="n">
-        <v>109856</v>
+        <v>9491</v>
       </c>
       <c r="I6" t="n">
-        <v>11076</v>
+        <v>90</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>71548</v>
+        <v>6603</v>
       </c>
       <c r="Z6" t="n">
-        <v>58765</v>
+        <v>5375</v>
       </c>
       <c r="AA6" t="n">
-        <v>120515</v>
+        <v>11116</v>
       </c>
       <c r="AB6" t="n">
-        <v>649524</v>
+        <v>59360</v>
       </c>
       <c r="AC6" t="n">
-        <v>76925</v>
+        <v>7024</v>
       </c>
       <c r="AD6" t="n">
-        <v>5292</v>
+        <v>482</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>96</v>
+        <v>29</v>
       </c>
       <c r="D7" t="n">
-        <v>68163</v>
+        <v>14667</v>
       </c>
       <c r="E7" t="n">
-        <v>516199</v>
+        <v>81920</v>
       </c>
       <c r="F7" t="n">
-        <v>1190277</v>
+        <v>155640</v>
       </c>
       <c r="G7" t="n">
-        <v>382423</v>
+        <v>66715</v>
       </c>
       <c r="H7" t="n">
-        <v>3213376</v>
+        <v>193133</v>
       </c>
       <c r="I7" t="n">
-        <v>241827</v>
+        <v>399</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>187</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>8907</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>327984</v>
+        <v>30153</v>
       </c>
       <c r="AB7" t="n">
-        <v>83851</v>
+        <v>7720</v>
       </c>
       <c r="AC7" t="n">
-        <v>5058909</v>
+        <v>461747</v>
       </c>
       <c r="AD7" t="n">
-        <v>132523</v>
+        <v>12065</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>170</v>
+        <v>84</v>
       </c>
       <c r="D8" t="n">
-        <v>4824</v>
+        <v>1285</v>
       </c>
       <c r="E8" t="n">
-        <v>52630</v>
+        <v>9795</v>
       </c>
       <c r="F8" t="n">
-        <v>118662</v>
+        <v>22201</v>
       </c>
       <c r="G8" t="n">
-        <v>60149</v>
+        <v>14914</v>
       </c>
       <c r="H8" t="n">
-        <v>723918</v>
+        <v>144968</v>
       </c>
       <c r="I8" t="n">
-        <v>1168192</v>
+        <v>685</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>308</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>891</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>3647</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>2927</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>138752</v>
+        <v>12696</v>
       </c>
       <c r="AD8" t="n">
-        <v>1982020</v>
+        <v>180527</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
